--- a/docs/INVERTA_UAT_Test_Cases_v1.0.xlsx
+++ b/docs/INVERTA_UAT_Test_Cases_v1.0.xlsx
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>main @ a606e4b</t>
+          <t>main @ (post bulk-import + restore-access fix)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -857,173 +857,191 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>• Run cases in ID order (A-01, A-02, …) unless a case says otherwise. A few cases must be run at a particular moment — E-05 says so explicitly — because passing a test is permanent and cannot be undone.</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Jalankan kasus sesuai urutan ID (A-01, A-02, …) kecuali kasus itu menyebutkan lain. Beberapa kasus harus dijalankan pada saat tertentu — E-05 menyebutkannya — karena lulus tes bersifat permanen dan tidak bisa dibatalkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>3. NOT part of this build — do not raise bugs for these</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Bukan bagian dari build ini — jangan laporkan sebagai bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>✗ Final exam, scoring and certificates</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>The final assessment has 0 questions, and the bank has 15 where the format needs 140. The whole final-exam chain cannot be tested yet.</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Tes akhir belum punya soal (0), bank soal baru 15 dari 140. Seluruh alur tes akhir belum bisa diuji.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>✗ "Lanjutkan dengan Google" button on the login page</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>The button is visible but Google sign-in was never connected. It will not work.</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Tombol terlihat tetapi login Google belum tersambung. Tidak akan berfungsi.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>✗ Video content</t>
+          <t>✗ Final exam, scoring and certificates</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Every session plays the same sample clip, on purpose. Real video is not connected yet.</t>
+          <t>The final assessment has 0 questions, and the bank has 15 where the format needs 140. The whole final-exam chain cannot be tested yet.</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Semua sesi memutar klip contoh yang sama, memang disengaja. Video asli belum tersambung.</t>
+          <t>Tes akhir belum punya soal (0), bank soal baru 15 dari 140. Seluruh alur tes akhir belum bisa diuji.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>✗ Real payment</t>
+          <t>✗ "Lanjutkan dengan Google" button on the login page</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Payment uses a built-in simulator. No real money, no real gateway.</t>
+          <t>The button is visible but Google sign-in was never connected. It will not work.</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Pembayaran memakai simulator bawaan. Bukan uang atau gateway sungguhan.</t>
+          <t>Tombol terlihat tetapi login Google belum tersambung. Tidak akan berfungsi.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>✗ Emails</t>
+          <t>✗ Video content</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Emails are written to the server log, not sent. You will not receive anything.</t>
+          <t>Every session plays the same sample clip, on purpose. Real video is not connected yet.</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Email ditulis ke log server, tidak dikirim. Anda tidak akan menerima apa pun.</t>
+          <t>Semua sesi memutar klip contoh yang sama, memang disengaja. Video asli belum tersambung.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
+          <t>✗ Real payment</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Payment uses a built-in simulator. No real money, no real gateway.</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Pembayaran memakai simulator bawaan. Bukan uang atau gateway sungguhan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>✗ Emails</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Emails are written to the server log, not sent. You will not receive anything.</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Email ditulis ke log server, tidak dikirim. Anda tidak akan menerima apa pun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
           <t>✗ Listening audio voice quality</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>The sample audio is computer-generated on purpose. Robotic voice is expected, not a bug.</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Audio contoh sengaja dibuat komputer. Suara robot itu wajar, bukan bug.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>4. What is in this pack / Isi paket ini</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>Functional cases / Kasus fungsional (A–K)</t>
         </is>
       </c>
-      <c r="B42" s="23" t="n">
+      <c r="B44" s="23" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Negative &amp; edge cases / Kasus negatif &amp; tepi (N)</t>
         </is>
       </c>
-      <c r="B43" s="23" t="n">
+      <c r="B45" s="23" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B44" s="23" t="n">
+      <c r="B46" s="23" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="47" ht="30" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Negative cases check that the app REFUSES things correctly. For these, a refusal is a Pass.
 Kasus negatif menguji bahwa aplikasi MENOLAK dengan benar. Untuk kasus ini, penolakan berarti Pass.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Cases marked SECURITY (N-05, N-06, N-07, E-02) must be reported to the team IMMEDIATELY if they fail.
 Kasus bertanda SECURITY (N-05, N-06, N-07, E-02) harus SEGERA dilaporkan ke tim bila gagal.</t>
@@ -2239,24 +2257,26 @@
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>You have just failed the test in E-03.</t>
+          <t>Run this IMMEDIATELY after E-03, BEFORE you run E-04. Stay on the same screen — do not reload the page or navigate away. Once the test has been passed (E-04) it is complete and this case can no longer be run; to redo it you need a learner who has not passed yet.</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>Anda baru saja gagal pada E-03.</t>
+          <t>Kerjakan SEGERA setelah E-03, SEBELUM mengerjakan E-04. Tetap di layar yang sama — jangan muat ulang halaman atau berpindah halaman. Jika tes sudah pernah lulus (E-04), tes itu selesai dan kasus ini tidak bisa dijalankan lagi; perlu siswa lain yang belum lulus.</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>1. After the failed result, look for a retry control ("Coba lagi").
-2. Click it and check the test opens again.</t>
+          <t>1. On the failed result from E-03, without leaving the page, find the "Coba lagi" button at the bottom right of the test panel.
+2. Click it. The 15 questions should reappear, unanswered.
+3. Check the button did NOT read "Batas percobaan tercapai".</t>
         </is>
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>1. Setelah hasil gagal, cari tombol ulang ("Coba lagi").
-2. Klik dan pastikan tes terbuka kembali.</t>
+          <t>1. Pada hasil tidak lulus dari E-03, tanpa meninggalkan halaman, cari tombol "Coba lagi" di kanan bawah panel tes.
+2. Klik tombol itu. Ke-15 soal harus muncul kembali dalam keadaan kosong.
+3. Pastikan tombol TIDAK bertuliskan "Batas percobaan tercapai".</t>
         </is>
       </c>
       <c r="I20" s="16" t="inlineStr">
@@ -3134,24 +3154,28 @@
       </c>
       <c r="G35" s="19" t="inlineStr">
         <is>
-          <t>1. Restore or re-grant access for siswa@test.local.
-2. Sign in as siswa@test.local and open the dashboard.</t>
+          <t>1. Go to https://inverta.recosta.id/admin/enrollments and find siswa@test.local. Its status is "Dicabut".
+2. Click "Pulihkan" on that row and confirm.
+3. Check the status returns to "Aktif".
+4. Sign in as siswa@test.local and open the dashboard.</t>
         </is>
       </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
-          <t>1. Pulihkan atau berikan kembali akses untuk siswa@test.local.
-2. Masuk sebagai siswa@test.local dan buka dashboard.</t>
+          <t>1. Buka https://inverta.recosta.id/admin/enrollments lalu cari siswa@test.local. Statusnya "Dicabut".
+2. Klik "Pulihkan" pada baris tersebut lalu konfirmasi.
+3. Pastikan status kembali menjadi "Aktif".
+4. Masuk sebagai siswa@test.local dan buka dashboard.</t>
         </is>
       </c>
       <c r="I35" s="19" t="inlineStr">
         <is>
-          <t>The learner can reach the programme again, and their earlier progress is still there.</t>
+          <t>The status returns to "Aktif" and the learner reaches the programme again, with their earlier progress and test attempts still there. The SAME enrollment is restored — no second enrollment row appears for that learner.</t>
         </is>
       </c>
       <c r="J35" s="19" t="inlineStr">
         <is>
-          <t>Siswa bisa membuka program lagi, dan progres sebelumnya masih ada.</t>
+          <t>Status kembali "Aktif" dan siswa bisa membuka program lagi, dengan progres serta riwayat percobaan tes yang lama masih ada. Pendaftaran yang SAMA dipulihkan — tidak muncul baris pendaftaran kedua untuk siswa itu.</t>
         </is>
       </c>
       <c r="K35" s="17" t="n"/>

--- a/docs/INVERTA_UAT_Test_Cases_v1.0.xlsx
+++ b/docs/INVERTA_UAT_Test_Cases_v1.0.xlsx
@@ -990,8 +990,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
@@ -1026,9 +1024,6 @@
         <is>
           <t>TOTAL</t>
         </is>
-      </c>
-      <c r="B46" s="23" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1"/>
@@ -2843,46 +2838,46 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>A question cannot be saved without a correct answer marked.</t>
+          <t>A question with no correct answer marked is refused by the server.</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Soal tidak bisa disimpan tanpa menandai jawaban benar.</t>
+          <t>Soal tanpa jawaban benar ditolak oleh server.</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>Signed in as admin.</t>
+          <t>Signed in as admin. NOTE: the question form always keeps one choice selected, so this state cannot be produced through the screen — that is by design. Check the form's behaviour instead.</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>Masuk sebagai admin.</t>
+          <t>Masuk sebagai admin. CATATAN: form soal selalu menyisakan satu pilihan tertandai, jadi kondisi ini tidak bisa dibuat lewat layar — itu memang disengaja. Periksa perilaku form-nya.</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>1. Go to https://inverta.recosta.id/admin/questions and start a new question.
-2. Fill the prompt and 4 choices, but do NOT mark any choice as correct.
-3. Try to save.</t>
+          <t>1. Go to https://inverta.recosta.id/admin/questions and click "+ Soal baru".
+2. Fill the prompt and all four choices.
+3. Try to leave every choice unmarked — click around the radio buttons and see whether any state has NO choice selected.</t>
         </is>
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>1. Buka https://inverta.recosta.id/admin/questions dan mulai soal baru.
-2. Isi pertanyaan dan 4 pilihan, tetapi JANGAN tandai jawaban benar.
-3. Coba simpan.</t>
+          <t>1. Buka https://inverta.recosta.id/admin/questions lalu klik "+ Soal baru".
+2. Isi pertanyaan dan keempat pilihan.
+3. Coba biarkan semua pilihan tidak tertandai — klik-klik tombol radio dan lihat apakah ada keadaan TANPA pilihan tertandai.</t>
         </is>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
-          <t>Saving is refused with a clear message telling you to mark a correct answer. The question is not created.</t>
+          <t>Exactly one choice is ALWAYS marked — there is no way to leave a question without a correct answer. The form prevents the mistake rather than letting you save and be told off. (The server refuses it too; that is covered by an automated test.)</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>Penyimpanan ditolak dengan pesan jelas agar menandai jawaban benar. Soal tidak dibuat.</t>
+          <t>Selalu ada tepat satu pilihan tertandai — tidak ada cara meninggalkan soal tanpa jawaban benar. Form mencegah kesalahannya, bukan membiarkan Anda menyimpan lalu ditegur. (Server juga menolaknya; itu sudah diuji otomatis.)</t>
         </is>
       </c>
       <c r="K30" s="17" t="n"/>
@@ -3983,22 +3978,22 @@
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>Answers survive a page refresh in the middle of the test.</t>
+          <t>Reloading mid-test does not consume an attempt or score you.</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Jawaban bertahan saat halaman dimuat ulang di tengah tes.</t>
+          <t>Memuat ulang di tengah tes tidak menghabiskan percobaan atau menilai Anda.</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>Session 1 test is open and not yet submitted.</t>
+          <t>Session 1 test is open and not yet submitted. NOTE: answers are only sent when you press "Kirim jawaban", so a reload CLEARS what you had ticked. That is expected — losing the ticks is not the bug this case looks for.</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>Tes sesi 1 terbuka dan belum dikirim.</t>
+          <t>Tes sesi 1 terbuka dan belum dikirim. CATATAN: jawaban baru dikirim saat Anda menekan "Kirim jawaban", jadi memuat ulang MENGHAPUS centang Anda. Itu wajar — hilangnya centang bukan bug yang dicari kasus ini.</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
@@ -4006,25 +4001,25 @@
           <t>1. Open the session 1 test.
 2. Answer the first 5 questions only. Do NOT submit.
 3. Press F5 to reload the page.
-4. Open the test again and look at questions 1 to 5.</t>
+4. Open the test again and check: is it still 15 unanswered questions, with no score shown and no attempt used?</t>
         </is>
       </c>
       <c r="H50" s="16" t="inlineStr">
         <is>
           <t>1. Buka tes sesi 1.
 2. Jawab 5 soal pertama saja. JANGAN kirim.
-3. Tekan F5 untuk memuat ulang.
-4. Buka lagi tesnya dan lihat soal 1 sampai 5.</t>
+3. Tekan F5 untuk memuat ulang halaman.
+4. Buka tes lagi dan periksa: apakah masih 15 soal kosong, tanpa skor dan tanpa percobaan terpakai?</t>
         </is>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
-          <t>You are still in the same attempt. The reload has not used up an extra attempt and has not scored you.</t>
+          <t>The test is simply open again with nothing answered. No score appears, no failed attempt is recorded, and the session is NOT completed. The ticks being gone is expected.</t>
         </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>Anda tetap pada percobaan yang sama. Muat ulang tidak menghabiskan percobaan tambahan dan tidak menilai Anda.</t>
+          <t>Tes hanya terbuka kembali tanpa jawaban. Tidak ada skor, tidak ada percobaan gagal yang tercatat, dan sesi TIDAK selesai. Hilangnya centang memang wajar.</t>
         </is>
       </c>
       <c r="K50" s="17" t="n"/>
@@ -4166,44 +4161,48 @@
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>Passing again after already passing does not break anything.</t>
+          <t>A passed session stays passed and does not skip ahead.</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>Lulus lagi setelah sebelumnya lulus tidak merusak apa pun.</t>
+          <t>Sesi yang sudah lulus tetap lulus dan tidak melompati sesi.</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>Session 1 has already been passed (E-04 done).</t>
+          <t>Session 1 has already been passed (E-04 done). NOTE: once a test is passed it is complete and the questions do not reappear, so it cannot be taken a second time — that is intended, not a bug.</t>
         </is>
       </c>
       <c r="F53" s="19" t="inlineStr">
         <is>
-          <t>Sesi 1 sudah pernah lulus (E-04 selesai).</t>
+          <t>Sesi 1 sudah lulus (E-04 selesai). CATATAN: setelah lulus, tes itu selesai dan soalnya tidak muncul lagi, jadi tidak bisa dikerjakan kedua kali — itu memang disengaja, bukan bug.</t>
         </is>
       </c>
       <c r="G53" s="19" t="inlineStr">
         <is>
-          <t>1. Open the session 1 test again and pass it a second time.
-2. Return to the programme page and check sessions 1, 2 and 3.</t>
+          <t>1. Open session 1 again.
+2. Check what the test panel shows.
+3. Return to the programme page and look at sessions 1, 2 and 3.
+4. Reload the page and look again.</t>
         </is>
       </c>
       <c r="H53" s="19" t="inlineStr">
         <is>
-          <t>1. Buka lagi tes sesi 1 dan lulus untuk kedua kalinya.
-2. Kembali ke halaman program dan periksa sesi 1, 2 dan 3.</t>
+          <t>1. Buka kembali sesi 1.
+2. Perhatikan yang ditampilkan panel tes.
+3. Kembali ke halaman program dan lihat sesi 1, 2 dan 3.
+4. Muat ulang halaman dan lihat lagi.</t>
         </is>
       </c>
       <c r="I53" s="19" t="inlineStr">
         <is>
-          <t>Session 1 stays Completed and session 2 stays open. Session 3 does NOT unlock. Passing twice must not skip a session.</t>
+          <t>The panel shows the passed state with the score, NOT the 15 questions again. Session 1 stays Completed, session 2 stays open, and session 3 stays LOCKED. Reloading changes none of it.</t>
         </is>
       </c>
       <c r="J53" s="19" t="inlineStr">
         <is>
-          <t>Sesi 1 tetap Completed dan sesi 2 tetap terbuka. Sesi 3 TIDAK terbuka. Lulus dua kali tidak boleh melewati sesi.</t>
+          <t>Panel menampilkan keadaan lulus beserta skor, BUKAN ke-15 soal lagi. Sesi 1 tetap Completed, sesi 2 tetap terbuka, dan sesi 3 tetap TERKUNCI. Memuat ulang tidak mengubah apa pun.</t>
         </is>
       </c>
       <c r="K53" s="17" t="n"/>
@@ -4636,12 +4635,12 @@
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>A question cannot be saved with fewer than two answer choices.</t>
+          <t>A question can never be reduced to fewer than two answer choices.</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>Soal tidak bisa disimpan dengan pilihan jawaban kurang dari dua.</t>
+          <t>Soal tidak pernah bisa dikurangi hingga kurang dari dua pilihan jawaban.</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -4656,26 +4655,28 @@
       </c>
       <c r="G61" s="19" t="inlineStr">
         <is>
-          <t>1. Go to https://inverta.recosta.id/admin/questions and start a new question.
-2. Fill the prompt but leave only ONE answer choice filled in (use "Hapus pilihan" to remove the others).
-3. Try to save.</t>
+          <t>1. Go to https://inverta.recosta.id/admin/questions and click "+ Soal baru".
+2. The form starts with two choices. Add a third with "+ Tambah pilihan".
+3. Remove choices one by one using the × button beside each.
+4. Keep going until you cannot remove any more.</t>
         </is>
       </c>
       <c r="H61" s="19" t="inlineStr">
         <is>
-          <t>1. Buka https://inverta.recosta.id/admin/questions dan mulai soal baru.
-2. Isi pertanyaan tapi sisakan HANYA SATU pilihan jawaban (pakai "Hapus pilihan" untuk menghapus lainnya).
-3. Coba simpan.</t>
+          <t>1. Buka https://inverta.recosta.id/admin/questions lalu klik "+ Soal baru".
+2. Form dimulai dengan dua pilihan. Tambah satu lagi dengan "+ Tambah pilihan".
+3. Hapus pilihan satu per satu memakai tombol × di sebelahnya.
+4. Terus sampai tidak bisa menghapus lagi.</t>
         </is>
       </c>
       <c r="I61" s="19" t="inlineStr">
         <is>
-          <t>Saving is refused with a message that at least two choices are required. The question is not created.</t>
+          <t>You can delete down to TWO choices and no further — at two, the × buttons disappear. Saving also stays disabled while any choice is left empty. (The server refuses a one-choice question too; that is covered by an automated test.)</t>
         </is>
       </c>
       <c r="J61" s="19" t="inlineStr">
         <is>
-          <t>Penyimpanan ditolak dengan pesan minimal dua pilihan. Soal tidak dibuat.</t>
+          <t>Anda bisa menghapus sampai DUA pilihan dan tidak lebih — pada dua pilihan, tombol × hilang. Tombol simpan juga tetap nonaktif selama ada pilihan yang kosong. (Server juga menolak soal berpilihan satu; itu sudah diuji otomatis.)</t>
         </is>
       </c>
       <c r="K61" s="17" t="n"/>
